--- a/py_solution/result1.xlsx
+++ b/py_solution/result1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="问题3" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="问题3结果" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -424,67 +424,67 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>航向角rad</t>
+          <t>航向角(rad)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>航向角°</t>
+          <t>航向角(°)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>速度m/s</t>
+          <t>飞行速度(m/s)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>弹编号</t>
+          <t>烟幕弹编号</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>投放时间s</t>
+          <t>投放时间(s)</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>延时s</t>
+          <t>起爆延时(s)</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>投放X</t>
+          <t>投放点X</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>投放Y</t>
+          <t>投放点Y</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>投放Z</t>
+          <t>投放点Z</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>起爆X</t>
+          <t>起爆点X</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>起爆Y</t>
+          <t>起爆点Y</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>起爆Z</t>
+          <t>起爆点Z</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>总时长s</t>
+          <t>总有效遮蔽时长(s)</t>
         </is>
       </c>
     </row>
@@ -495,25 +495,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.141593</v>
+        <v>3.110997</v>
       </c>
       <c r="C2" t="n">
-        <v>180</v>
+        <v>178.247</v>
       </c>
       <c r="D2" t="n">
-        <v>80</v>
+        <v>83.81</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0784</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>2.7405</v>
+        <v>2.91</v>
       </c>
       <c r="H2" t="n">
-        <v>17793.73</v>
+        <v>17800</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -522,16 +522,16 @@
         <v>1800</v>
       </c>
       <c r="K2" t="n">
-        <v>17574.49</v>
+        <v>17556.22</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>7.46</v>
       </c>
       <c r="M2" t="n">
-        <v>1763.2</v>
+        <v>1758.51</v>
       </c>
       <c r="N2" t="n">
-        <v>4.9</v>
+        <v>5.555</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.141593</v>
+        <v>3.110997</v>
       </c>
       <c r="C3" t="n">
-        <v>180</v>
+        <v>178.247</v>
       </c>
       <c r="D3" t="n">
-        <v>80</v>
+        <v>83.81</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0841</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>3.5721</v>
+        <v>2.8847</v>
       </c>
       <c r="H3" t="n">
-        <v>17713.27</v>
+        <v>17716.22</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="J3" t="n">
         <v>1800</v>
       </c>
       <c r="K3" t="n">
-        <v>17427.5</v>
+        <v>17474.56</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>1737.48</v>
+        <v>1759.22</v>
       </c>
     </row>
     <row r="4">
@@ -584,40 +584,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.141593</v>
+        <v>3.110997</v>
       </c>
       <c r="C4" t="n">
-        <v>180</v>
+        <v>178.247</v>
       </c>
       <c r="D4" t="n">
-        <v>80</v>
+        <v>83.81</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>5.9235</v>
+        <v>2.0455</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9727</v>
+        <v>1.0562</v>
       </c>
       <c r="H4" t="n">
-        <v>17326.12</v>
+        <v>17628.64</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="J4" t="n">
         <v>1800</v>
       </c>
       <c r="K4" t="n">
-        <v>17168.3</v>
+        <v>17540.15</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="M4" t="n">
-        <v>1780.93</v>
+        <v>1794.53</v>
       </c>
     </row>
   </sheetData>
